--- a/Bin/A-QIP-WS009-02B.xlsx
+++ b/Bin/A-QIP-WS009-02B.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\lys_erp\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B119C6-E08F-4AF1-A115-E124D1571F3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="75" windowWidth="9555" windowHeight="3660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$I$17</definedName>
@@ -213,7 +212,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6">
     <font>
       <sz val="11"/>
@@ -366,29 +365,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -411,9 +410,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -434,9 +430,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -474,9 +470,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -511,7 +507,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -546,7 +542,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -719,7 +715,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -749,38 +745,38 @@
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" ht="48" customHeight="1">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5" t="s">
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="2"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:10" ht="48" customHeight="1">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="2"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:10" ht="105" customHeight="1">
       <c r="A4" s="11" t="s">
@@ -822,7 +818,7 @@
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
-      <c r="J6" s="6"/>
+      <c r="J6" s="5"/>
     </row>
     <row r="7" spans="1:10" ht="30.75" customHeight="1">
       <c r="A7" s="10" t="s">
@@ -836,20 +832,20 @@
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
-      <c r="J7" s="6"/>
+      <c r="J7" s="5"/>
     </row>
     <row r="8" spans="1:10" ht="30.75" customHeight="1">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
       <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10" ht="141" customHeight="1">
@@ -864,111 +860,111 @@
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
       <c r="I9" s="14"/>
-      <c r="J9" s="2"/>
+      <c r="J9" s="1"/>
     </row>
     <row r="10" spans="1:10" ht="30" customHeight="1">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5" t="s">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5" t="s">
+      <c r="E10" s="7"/>
+      <c r="F10" s="7" t="s">
         <v>14</v>
       </c>
       <c r="G10" s="8"/>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="2"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="1"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="6"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="5"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="6"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="5"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="6"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="5"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="6"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="5"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="6"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="5"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="6"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="5"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="6"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -999,25 +995,9 @@
   <pageMargins left="0.15748031496062992" right="0.15748031496062992" top="0.19685039370078741" bottom="0.11811023622047245" header="0" footer="0.15748031496062992"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddFooter>&amp;RA-QIP-WS009-02B</oddFooter>
+    <oddFooter xml:space="preserve">&amp;RA-QIP-WS009-02B
+QIP/VII/18/01
+</oddFooter>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>